--- a/karyawan-contoh.xlsx
+++ b/karyawan-contoh.xlsx
@@ -55,11 +55,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,13 +426,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D500"/>
+  <dimension ref="A1:F500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -455,6 +458,16 @@
           <t>Admin</t>
         </is>
       </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Departemen</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -469,12 +482,22 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>111111</t>
+          <t>1111</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>ya</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TRACK, WHEEL</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>PLANT</t>
         </is>
       </c>
     </row>
@@ -491,10 +514,19 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>123456</t>
+          <t>1234</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>TRACK</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>PLANT</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n"/>
